--- a/PRECOS.xlsx
+++ b/PRECOS.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G859"/>
+  <dimension ref="A1:G872"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="7" max="7" width="20.7109375" style="2" customWidth="1"/>
@@ -14486,10 +14486,10 @@
         </is>
       </c>
       <c r="E457">
-        <v>2.93</v>
+        <v>2.78</v>
       </c>
       <c r="F457">
-        <v>-3.3</v>
+        <v>-8.25</v>
       </c>
       <c r="G457" s="2">
         <v>46174</v>
@@ -14517,10 +14517,10 @@
         </is>
       </c>
       <c r="E458">
-        <v>5.82</v>
+        <v>3.67</v>
       </c>
       <c r="F458">
-        <v>70.18000000000001</v>
+        <v>7.31</v>
       </c>
       <c r="G458" s="2">
         <v>46174</v>
@@ -14579,10 +14579,10 @@
         </is>
       </c>
       <c r="E460">
-        <v>7.94</v>
+        <v>5.89</v>
       </c>
       <c r="F460">
-        <v>104.11</v>
+        <v>51.41</v>
       </c>
       <c r="G460" s="2">
         <v>46174</v>
@@ -14610,10 +14610,10 @@
         </is>
       </c>
       <c r="E461">
-        <v>23.58</v>
+        <v>22.49</v>
       </c>
       <c r="F461">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="G461" s="2">
         <v>46174</v>
@@ -14641,10 +14641,10 @@
         </is>
       </c>
       <c r="E462">
-        <v>49.02</v>
+        <v>47.59</v>
       </c>
       <c r="F462">
-        <v>1.16</v>
+        <v>-1.8</v>
       </c>
       <c r="G462" s="2">
         <v>46174</v>
@@ -14672,10 +14672,10 @@
         </is>
       </c>
       <c r="E463">
-        <v>3.17</v>
+        <v>3.1</v>
       </c>
       <c r="F463">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="G463" s="2">
         <v>46174</v>
@@ -14703,10 +14703,10 @@
         </is>
       </c>
       <c r="E464">
-        <v>5.39</v>
+        <v>4.59</v>
       </c>
       <c r="F464">
-        <v>20.85</v>
+        <v>2.91</v>
       </c>
       <c r="G464" s="2">
         <v>46174</v>
@@ -14734,10 +14734,10 @@
         </is>
       </c>
       <c r="E465">
-        <v>5.34</v>
+        <v>5.19</v>
       </c>
       <c r="F465">
-        <v>-2.2</v>
+        <v>-4.95</v>
       </c>
       <c r="G465" s="2">
         <v>46174</v>
@@ -14765,10 +14765,10 @@
         </is>
       </c>
       <c r="E466">
-        <v>28.4</v>
+        <v>28.19</v>
       </c>
       <c r="F466">
-        <v>3.46</v>
+        <v>2.7</v>
       </c>
       <c r="G466" s="2">
         <v>46174</v>
@@ -14796,10 +14796,10 @@
         </is>
       </c>
       <c r="E467">
-        <v>14.89</v>
+        <v>13.89</v>
       </c>
       <c r="F467">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="G467" s="2">
         <v>46174</v>
@@ -14827,10 +14827,10 @@
         </is>
       </c>
       <c r="E468">
-        <v>11.23</v>
+        <v>8.49</v>
       </c>
       <c r="F468">
-        <v>125.05</v>
+        <v>70.14</v>
       </c>
       <c r="G468" s="2">
         <v>46174</v>
@@ -14858,10 +14858,10 @@
         </is>
       </c>
       <c r="E469">
-        <v>9.01</v>
+        <v>7.86</v>
       </c>
       <c r="F469">
-        <v>19.81</v>
+        <v>4.52</v>
       </c>
       <c r="G469" s="2">
         <v>46174</v>
@@ -23151,7 +23151,7 @@
     <row r="743">
       <c r="A743" t="inlineStr">
         <is>
-          <t>Bombinhas</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="B743" t="inlineStr">
@@ -23161,7 +23161,7 @@
       </c>
       <c r="C743" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D743" t="inlineStr">
@@ -23170,16 +23170,19 @@
         </is>
       </c>
       <c r="E743">
-        <v>3.17</v>
+        <v>3.49</v>
+      </c>
+      <c r="F743">
+        <v>2.65</v>
       </c>
       <c r="G743" s="2">
-        <v>46082</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="744">
       <c r="A744" t="inlineStr">
         <is>
-          <t>Bombinhas</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="B744" t="inlineStr">
@@ -23189,7 +23192,7 @@
       </c>
       <c r="C744" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D744" t="inlineStr">
@@ -23198,16 +23201,19 @@
         </is>
       </c>
       <c r="E744">
-        <v>4.45</v>
+        <v>3.28</v>
+      </c>
+      <c r="F744">
+        <v>-19.61</v>
       </c>
       <c r="G744" s="2">
-        <v>46082</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="745">
       <c r="A745" t="inlineStr">
         <is>
-          <t>Bombinhas</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="B745" t="inlineStr">
@@ -23217,7 +23223,7 @@
       </c>
       <c r="C745" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D745" t="inlineStr">
@@ -23226,16 +23232,19 @@
         </is>
       </c>
       <c r="E745">
-        <v>5.82</v>
+        <v>5.52</v>
+      </c>
+      <c r="F745">
+        <v>-30.21</v>
       </c>
       <c r="G745" s="2">
-        <v>46082</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="746">
       <c r="A746" t="inlineStr">
         <is>
-          <t>Bombinhas</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="B746" t="inlineStr">
@@ -23245,7 +23254,7 @@
       </c>
       <c r="C746" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D746" t="inlineStr">
@@ -23254,16 +23263,19 @@
         </is>
       </c>
       <c r="E746">
-        <v>4.72</v>
+        <v>5.09</v>
+      </c>
+      <c r="F746">
+        <v>46.69</v>
       </c>
       <c r="G746" s="2">
-        <v>46082</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="747">
       <c r="A747" t="inlineStr">
         <is>
-          <t>Bombinhas</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="B747" t="inlineStr">
@@ -23273,7 +23285,7 @@
       </c>
       <c r="C747" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D747" t="inlineStr">
@@ -23282,16 +23294,19 @@
         </is>
       </c>
       <c r="E747">
-        <v>32.35</v>
+        <v>22.37</v>
+      </c>
+      <c r="F747">
+        <v>-26.8</v>
       </c>
       <c r="G747" s="2">
-        <v>46082</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="748">
       <c r="A748" t="inlineStr">
         <is>
-          <t>Bombinhas</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="B748" t="inlineStr">
@@ -23301,7 +23316,7 @@
       </c>
       <c r="C748" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D748" t="inlineStr">
@@ -23310,16 +23325,19 @@
         </is>
       </c>
       <c r="E748">
-        <v>48.44</v>
+        <v>55.26</v>
+      </c>
+      <c r="F748">
+        <v>19.61</v>
       </c>
       <c r="G748" s="2">
-        <v>46082</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="749">
       <c r="A749" t="inlineStr">
         <is>
-          <t>Bombinhas</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="B749" t="inlineStr">
@@ -23329,7 +23347,7 @@
       </c>
       <c r="C749" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D749" t="inlineStr">
@@ -23338,16 +23356,19 @@
         </is>
       </c>
       <c r="E749">
-        <v>3.81</v>
+        <v>3.13</v>
+      </c>
+      <c r="F749">
+        <v>-14.95</v>
       </c>
       <c r="G749" s="2">
-        <v>46082</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="750">
       <c r="A750" t="inlineStr">
         <is>
-          <t>Bombinhas</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="B750" t="inlineStr">
@@ -23357,7 +23378,7 @@
       </c>
       <c r="C750" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D750" t="inlineStr">
@@ -23366,16 +23387,19 @@
         </is>
       </c>
       <c r="E750">
-        <v>5.82</v>
+        <v>6.51</v>
+      </c>
+      <c r="F750">
+        <v>37.34</v>
       </c>
       <c r="G750" s="2">
-        <v>46082</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="751">
       <c r="A751" t="inlineStr">
         <is>
-          <t>Bombinhas</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="B751" t="inlineStr">
@@ -23385,7 +23409,7 @@
       </c>
       <c r="C751" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D751" t="inlineStr">
@@ -23394,16 +23418,19 @@
         </is>
       </c>
       <c r="E751">
-        <v>4.94</v>
+        <v>5.18</v>
+      </c>
+      <c r="F751">
+        <v>11.64</v>
       </c>
       <c r="G751" s="2">
-        <v>46082</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="752">
       <c r="A752" t="inlineStr">
         <is>
-          <t>Bombinhas</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="B752" t="inlineStr">
@@ -23413,7 +23440,7 @@
       </c>
       <c r="C752" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D752" t="inlineStr">
@@ -23422,16 +23449,19 @@
         </is>
       </c>
       <c r="E752">
-        <v>28.27</v>
+        <v>26.74</v>
+      </c>
+      <c r="F752">
+        <v>-6.99</v>
       </c>
       <c r="G752" s="2">
-        <v>46082</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="753">
       <c r="A753" t="inlineStr">
         <is>
-          <t>Bombinhas</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="B753" t="inlineStr">
@@ -23441,7 +23471,7 @@
       </c>
       <c r="C753" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D753" t="inlineStr">
@@ -23450,16 +23480,19 @@
         </is>
       </c>
       <c r="E753">
-        <v>16.95</v>
+        <v>15.29</v>
+      </c>
+      <c r="F753">
+        <v>-9.789999999999999</v>
       </c>
       <c r="G753" s="2">
-        <v>46082</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="754">
       <c r="A754" t="inlineStr">
         <is>
-          <t>Bombinhas</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="B754" t="inlineStr">
@@ -23469,7 +23502,7 @@
       </c>
       <c r="C754" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D754" t="inlineStr">
@@ -23478,16 +23511,19 @@
         </is>
       </c>
       <c r="E754">
-        <v>8.789999999999999</v>
+        <v>7.48</v>
+      </c>
+      <c r="F754">
+        <v>37.75</v>
       </c>
       <c r="G754" s="2">
-        <v>46082</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="755">
       <c r="A755" t="inlineStr">
         <is>
-          <t>Bombinhas</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="B755" t="inlineStr">
@@ -23497,7 +23533,7 @@
       </c>
       <c r="C755" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D755" t="inlineStr">
@@ -23506,10 +23542,13 @@
         </is>
       </c>
       <c r="E755">
-        <v>7.76</v>
+        <v>7.14</v>
+      </c>
+      <c r="F755">
+        <v>-3.77</v>
       </c>
       <c r="G755" s="2">
-        <v>46082</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="756">
@@ -23525,7 +23564,7 @@
       </c>
       <c r="C756" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D756" t="inlineStr">
@@ -23534,13 +23573,10 @@
         </is>
       </c>
       <c r="E756">
-        <v>3.4</v>
-      </c>
-      <c r="F756">
-        <v>7.26</v>
+        <v>3.17</v>
       </c>
       <c r="G756" s="2">
-        <v>46113</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="757">
@@ -23556,7 +23592,7 @@
       </c>
       <c r="C757" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D757" t="inlineStr">
@@ -23565,13 +23601,10 @@
         </is>
       </c>
       <c r="E757">
-        <v>4.15</v>
-      </c>
-      <c r="F757">
-        <v>-6.74</v>
+        <v>4.45</v>
       </c>
       <c r="G757" s="2">
-        <v>46113</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="758">
@@ -23587,7 +23620,7 @@
       </c>
       <c r="C758" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D758" t="inlineStr">
@@ -23596,13 +23629,10 @@
         </is>
       </c>
       <c r="E758">
-        <v>5.25</v>
-      </c>
-      <c r="F758">
-        <v>-9.789999999999999</v>
+        <v>5.82</v>
       </c>
       <c r="G758" s="2">
-        <v>46113</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="759">
@@ -23618,7 +23648,7 @@
       </c>
       <c r="C759" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D759" t="inlineStr">
@@ -23627,13 +23657,10 @@
         </is>
       </c>
       <c r="E759">
-        <v>7.46</v>
-      </c>
-      <c r="F759">
-        <v>58.05</v>
+        <v>4.72</v>
       </c>
       <c r="G759" s="2">
-        <v>46113</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="760">
@@ -23649,7 +23676,7 @@
       </c>
       <c r="C760" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D760" t="inlineStr">
@@ -23658,13 +23685,10 @@
         </is>
       </c>
       <c r="E760">
-        <v>31.37</v>
-      </c>
-      <c r="F760">
-        <v>-3.03</v>
+        <v>32.35</v>
       </c>
       <c r="G760" s="2">
-        <v>46113</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="761">
@@ -23680,7 +23704,7 @@
       </c>
       <c r="C761" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D761" t="inlineStr">
@@ -23689,13 +23713,10 @@
         </is>
       </c>
       <c r="E761">
-        <v>48.68</v>
-      </c>
-      <c r="F761">
-        <v>0.5</v>
+        <v>48.44</v>
       </c>
       <c r="G761" s="2">
-        <v>46113</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="762">
@@ -23711,7 +23732,7 @@
       </c>
       <c r="C762" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D762" t="inlineStr">
@@ -23720,13 +23741,10 @@
         </is>
       </c>
       <c r="E762">
-        <v>3.76</v>
-      </c>
-      <c r="F762">
-        <v>-1.31</v>
+        <v>3.81</v>
       </c>
       <c r="G762" s="2">
-        <v>46113</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="763">
@@ -23742,7 +23760,7 @@
       </c>
       <c r="C763" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D763" t="inlineStr">
@@ -23751,13 +23769,10 @@
         </is>
       </c>
       <c r="E763">
-        <v>6.01</v>
-      </c>
-      <c r="F763">
-        <v>3.26</v>
+        <v>5.82</v>
       </c>
       <c r="G763" s="2">
-        <v>46113</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="764">
@@ -23773,7 +23788,7 @@
       </c>
       <c r="C764" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D764" t="inlineStr">
@@ -23782,13 +23797,10 @@
         </is>
       </c>
       <c r="E764">
-        <v>5.76</v>
-      </c>
-      <c r="F764">
-        <v>16.6</v>
+        <v>4.94</v>
       </c>
       <c r="G764" s="2">
-        <v>46113</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="765">
@@ -23804,7 +23816,7 @@
       </c>
       <c r="C765" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D765" t="inlineStr">
@@ -23813,13 +23825,10 @@
         </is>
       </c>
       <c r="E765">
-        <v>28.72</v>
-      </c>
-      <c r="F765">
-        <v>1.59</v>
+        <v>28.27</v>
       </c>
       <c r="G765" s="2">
-        <v>46113</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="766">
@@ -23835,7 +23844,7 @@
       </c>
       <c r="C766" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D766" t="inlineStr">
@@ -23844,13 +23853,10 @@
         </is>
       </c>
       <c r="E766">
-        <v>17.21</v>
-      </c>
-      <c r="F766">
-        <v>1.53</v>
+        <v>16.95</v>
       </c>
       <c r="G766" s="2">
-        <v>46113</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="767">
@@ -23866,7 +23872,7 @@
       </c>
       <c r="C767" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D767" t="inlineStr">
@@ -23875,13 +23881,10 @@
         </is>
       </c>
       <c r="E767">
-        <v>10.63</v>
-      </c>
-      <c r="F767">
-        <v>20.93</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="G767" s="2">
-        <v>46113</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="768">
@@ -23897,7 +23900,7 @@
       </c>
       <c r="C768" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D768" t="inlineStr">
@@ -23906,13 +23909,10 @@
         </is>
       </c>
       <c r="E768">
-        <v>7.71</v>
-      </c>
-      <c r="F768">
-        <v>-0.64</v>
+        <v>7.76</v>
       </c>
       <c r="G768" s="2">
-        <v>46113</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="769">
@@ -23928,7 +23928,7 @@
       </c>
       <c r="C769" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D769" t="inlineStr">
@@ -23937,13 +23937,13 @@
         </is>
       </c>
       <c r="E769">
-        <v>3.39</v>
+        <v>3.4</v>
       </c>
       <c r="F769">
-        <v>-0.29</v>
+        <v>7.26</v>
       </c>
       <c r="G769" s="2">
-        <v>46143</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="770">
@@ -23959,7 +23959,7 @@
       </c>
       <c r="C770" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D770" t="inlineStr">
@@ -23968,13 +23968,13 @@
         </is>
       </c>
       <c r="E770">
-        <v>4.17</v>
+        <v>4.15</v>
       </c>
       <c r="F770">
-        <v>0.48</v>
+        <v>-6.74</v>
       </c>
       <c r="G770" s="2">
-        <v>46143</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="771">
@@ -23990,7 +23990,7 @@
       </c>
       <c r="C771" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D771" t="inlineStr">
@@ -23999,13 +23999,13 @@
         </is>
       </c>
       <c r="E771">
-        <v>6.63</v>
+        <v>5.25</v>
       </c>
       <c r="F771">
-        <v>26.29</v>
+        <v>-9.789999999999999</v>
       </c>
       <c r="G771" s="2">
-        <v>46143</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="772">
@@ -24021,7 +24021,7 @@
       </c>
       <c r="C772" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D772" t="inlineStr">
@@ -24030,13 +24030,13 @@
         </is>
       </c>
       <c r="E772">
-        <v>8.99</v>
+        <v>7.46</v>
       </c>
       <c r="F772">
-        <v>20.51</v>
+        <v>58.05</v>
       </c>
       <c r="G772" s="2">
-        <v>46143</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="773">
@@ -24052,7 +24052,7 @@
       </c>
       <c r="C773" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D773" t="inlineStr">
@@ -24061,13 +24061,13 @@
         </is>
       </c>
       <c r="E773">
-        <v>28.77</v>
+        <v>31.37</v>
       </c>
       <c r="F773">
-        <v>-8.289999999999999</v>
+        <v>-3.03</v>
       </c>
       <c r="G773" s="2">
-        <v>46143</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="774">
@@ -24083,7 +24083,7 @@
       </c>
       <c r="C774" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D774" t="inlineStr">
@@ -24092,13 +24092,13 @@
         </is>
       </c>
       <c r="E774">
-        <v>50.03</v>
+        <v>48.68</v>
       </c>
       <c r="F774">
-        <v>2.77</v>
+        <v>0.5</v>
       </c>
       <c r="G774" s="2">
-        <v>46143</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="775">
@@ -24114,7 +24114,7 @@
       </c>
       <c r="C775" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D775" t="inlineStr">
@@ -24123,13 +24123,13 @@
         </is>
       </c>
       <c r="E775">
-        <v>3.51</v>
+        <v>3.76</v>
       </c>
       <c r="F775">
-        <v>-6.65</v>
+        <v>-1.31</v>
       </c>
       <c r="G775" s="2">
-        <v>46143</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="776">
@@ -24145,7 +24145,7 @@
       </c>
       <c r="C776" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D776" t="inlineStr">
@@ -24154,13 +24154,13 @@
         </is>
       </c>
       <c r="E776">
-        <v>5.9</v>
+        <v>6.01</v>
       </c>
       <c r="F776">
-        <v>-1.83</v>
+        <v>3.26</v>
       </c>
       <c r="G776" s="2">
-        <v>46143</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="777">
@@ -24176,7 +24176,7 @@
       </c>
       <c r="C777" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D777" t="inlineStr">
@@ -24185,13 +24185,13 @@
         </is>
       </c>
       <c r="E777">
-        <v>5.66</v>
+        <v>5.76</v>
       </c>
       <c r="F777">
-        <v>-1.74</v>
+        <v>16.6</v>
       </c>
       <c r="G777" s="2">
-        <v>46143</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="778">
@@ -24207,7 +24207,7 @@
       </c>
       <c r="C778" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D778" t="inlineStr">
@@ -24216,13 +24216,13 @@
         </is>
       </c>
       <c r="E778">
-        <v>28.67</v>
+        <v>28.72</v>
       </c>
       <c r="F778">
-        <v>-0.17</v>
+        <v>1.59</v>
       </c>
       <c r="G778" s="2">
-        <v>46143</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="779">
@@ -24238,7 +24238,7 @@
       </c>
       <c r="C779" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D779" t="inlineStr">
@@ -24247,13 +24247,13 @@
         </is>
       </c>
       <c r="E779">
-        <v>17.56</v>
+        <v>17.21</v>
       </c>
       <c r="F779">
-        <v>2.03</v>
+        <v>1.53</v>
       </c>
       <c r="G779" s="2">
-        <v>46143</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="780">
@@ -24269,7 +24269,7 @@
       </c>
       <c r="C780" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D780" t="inlineStr">
@@ -24278,13 +24278,13 @@
         </is>
       </c>
       <c r="E780">
-        <v>13.59</v>
+        <v>10.63</v>
       </c>
       <c r="F780">
-        <v>27.85</v>
+        <v>20.93</v>
       </c>
       <c r="G780" s="2">
-        <v>46143</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="781">
@@ -24300,7 +24300,7 @@
       </c>
       <c r="C781" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D781" t="inlineStr">
@@ -24309,19 +24309,19 @@
         </is>
       </c>
       <c r="E781">
-        <v>7.44</v>
+        <v>7.71</v>
       </c>
       <c r="F781">
-        <v>-3.5</v>
+        <v>-0.64</v>
       </c>
       <c r="G781" s="2">
-        <v>46143</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="782">
       <c r="A782" t="inlineStr">
         <is>
-          <t>Indaial</t>
+          <t>Bombinhas</t>
         </is>
       </c>
       <c r="B782" t="inlineStr">
@@ -24331,7 +24331,7 @@
       </c>
       <c r="C782" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="D782" t="inlineStr">
@@ -24340,16 +24340,19 @@
         </is>
       </c>
       <c r="E782">
-        <v>3.72</v>
+        <v>3.39</v>
+      </c>
+      <c r="F782">
+        <v>-0.29</v>
       </c>
       <c r="G782" s="2">
-        <v>46113</v>
+        <v>46143</v>
       </c>
     </row>
     <row r="783">
       <c r="A783" t="inlineStr">
         <is>
-          <t>Indaial</t>
+          <t>Bombinhas</t>
         </is>
       </c>
       <c r="B783" t="inlineStr">
@@ -24359,7 +24362,7 @@
       </c>
       <c r="C783" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="D783" t="inlineStr">
@@ -24368,16 +24371,19 @@
         </is>
       </c>
       <c r="E783">
-        <v>3.75</v>
+        <v>4.17</v>
+      </c>
+      <c r="F783">
+        <v>0.48</v>
       </c>
       <c r="G783" s="2">
-        <v>46113</v>
+        <v>46143</v>
       </c>
     </row>
     <row r="784">
       <c r="A784" t="inlineStr">
         <is>
-          <t>Indaial</t>
+          <t>Bombinhas</t>
         </is>
       </c>
       <c r="B784" t="inlineStr">
@@ -24387,7 +24393,7 @@
       </c>
       <c r="C784" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="D784" t="inlineStr">
@@ -24396,16 +24402,19 @@
         </is>
       </c>
       <c r="E784">
-        <v>6.18</v>
+        <v>6.63</v>
+      </c>
+      <c r="F784">
+        <v>26.29</v>
       </c>
       <c r="G784" s="2">
-        <v>46113</v>
+        <v>46143</v>
       </c>
     </row>
     <row r="785">
       <c r="A785" t="inlineStr">
         <is>
-          <t>Indaial</t>
+          <t>Bombinhas</t>
         </is>
       </c>
       <c r="B785" t="inlineStr">
@@ -24415,7 +24424,7 @@
       </c>
       <c r="C785" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="D785" t="inlineStr">
@@ -24424,16 +24433,19 @@
         </is>
       </c>
       <c r="E785">
-        <v>4.26</v>
+        <v>8.99</v>
+      </c>
+      <c r="F785">
+        <v>20.51</v>
       </c>
       <c r="G785" s="2">
-        <v>46113</v>
+        <v>46143</v>
       </c>
     </row>
     <row r="786">
       <c r="A786" t="inlineStr">
         <is>
-          <t>Indaial</t>
+          <t>Bombinhas</t>
         </is>
       </c>
       <c r="B786" t="inlineStr">
@@ -24443,7 +24455,7 @@
       </c>
       <c r="C786" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="D786" t="inlineStr">
@@ -24452,16 +24464,19 @@
         </is>
       </c>
       <c r="E786">
-        <v>28.61</v>
+        <v>28.77</v>
+      </c>
+      <c r="F786">
+        <v>-8.289999999999999</v>
       </c>
       <c r="G786" s="2">
-        <v>46113</v>
+        <v>46143</v>
       </c>
     </row>
     <row r="787">
       <c r="A787" t="inlineStr">
         <is>
-          <t>Indaial</t>
+          <t>Bombinhas</t>
         </is>
       </c>
       <c r="B787" t="inlineStr">
@@ -24471,7 +24486,7 @@
       </c>
       <c r="C787" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="D787" t="inlineStr">
@@ -24480,16 +24495,19 @@
         </is>
       </c>
       <c r="E787">
-        <v>52.79</v>
+        <v>50.03</v>
+      </c>
+      <c r="F787">
+        <v>2.77</v>
       </c>
       <c r="G787" s="2">
-        <v>46113</v>
+        <v>46143</v>
       </c>
     </row>
     <row r="788">
       <c r="A788" t="inlineStr">
         <is>
-          <t>Indaial</t>
+          <t>Bombinhas</t>
         </is>
       </c>
       <c r="B788" t="inlineStr">
@@ -24499,7 +24517,7 @@
       </c>
       <c r="C788" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="D788" t="inlineStr">
@@ -24508,16 +24526,19 @@
         </is>
       </c>
       <c r="E788">
-        <v>3.41</v>
+        <v>3.51</v>
+      </c>
+      <c r="F788">
+        <v>-6.65</v>
       </c>
       <c r="G788" s="2">
-        <v>46113</v>
+        <v>46143</v>
       </c>
     </row>
     <row r="789">
       <c r="A789" t="inlineStr">
         <is>
-          <t>Indaial</t>
+          <t>Bombinhas</t>
         </is>
       </c>
       <c r="B789" t="inlineStr">
@@ -24527,7 +24548,7 @@
       </c>
       <c r="C789" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="D789" t="inlineStr">
@@ -24536,16 +24557,19 @@
         </is>
       </c>
       <c r="E789">
-        <v>5.12</v>
+        <v>5.9</v>
+      </c>
+      <c r="F789">
+        <v>-1.83</v>
       </c>
       <c r="G789" s="2">
-        <v>46113</v>
+        <v>46143</v>
       </c>
     </row>
     <row r="790">
       <c r="A790" t="inlineStr">
         <is>
-          <t>Indaial</t>
+          <t>Bombinhas</t>
         </is>
       </c>
       <c r="B790" t="inlineStr">
@@ -24555,7 +24579,7 @@
       </c>
       <c r="C790" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="D790" t="inlineStr">
@@ -24564,16 +24588,19 @@
         </is>
       </c>
       <c r="E790">
-        <v>3.8</v>
+        <v>5.66</v>
+      </c>
+      <c r="F790">
+        <v>-1.74</v>
       </c>
       <c r="G790" s="2">
-        <v>46113</v>
+        <v>46143</v>
       </c>
     </row>
     <row r="791">
       <c r="A791" t="inlineStr">
         <is>
-          <t>Indaial</t>
+          <t>Bombinhas</t>
         </is>
       </c>
       <c r="B791" t="inlineStr">
@@ -24583,7 +24610,7 @@
       </c>
       <c r="C791" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="D791" t="inlineStr">
@@ -24592,16 +24619,19 @@
         </is>
       </c>
       <c r="E791">
-        <v>26.67</v>
+        <v>28.67</v>
+      </c>
+      <c r="F791">
+        <v>-0.17</v>
       </c>
       <c r="G791" s="2">
-        <v>46113</v>
+        <v>46143</v>
       </c>
     </row>
     <row r="792">
       <c r="A792" t="inlineStr">
         <is>
-          <t>Indaial</t>
+          <t>Bombinhas</t>
         </is>
       </c>
       <c r="B792" t="inlineStr">
@@ -24611,7 +24641,7 @@
       </c>
       <c r="C792" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="D792" t="inlineStr">
@@ -24620,16 +24650,19 @@
         </is>
       </c>
       <c r="E792">
-        <v>13.35</v>
+        <v>17.56</v>
+      </c>
+      <c r="F792">
+        <v>2.03</v>
       </c>
       <c r="G792" s="2">
-        <v>46113</v>
+        <v>46143</v>
       </c>
     </row>
     <row r="793">
       <c r="A793" t="inlineStr">
         <is>
-          <t>Indaial</t>
+          <t>Bombinhas</t>
         </is>
       </c>
       <c r="B793" t="inlineStr">
@@ -24639,7 +24672,7 @@
       </c>
       <c r="C793" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="D793" t="inlineStr">
@@ -24648,16 +24681,19 @@
         </is>
       </c>
       <c r="E793">
-        <v>12.98</v>
+        <v>13.59</v>
+      </c>
+      <c r="F793">
+        <v>27.85</v>
       </c>
       <c r="G793" s="2">
-        <v>46113</v>
+        <v>46143</v>
       </c>
     </row>
     <row r="794">
       <c r="A794" t="inlineStr">
         <is>
-          <t>Indaial</t>
+          <t>Bombinhas</t>
         </is>
       </c>
       <c r="B794" t="inlineStr">
@@ -24667,7 +24703,7 @@
       </c>
       <c r="C794" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="D794" t="inlineStr">
@@ -24676,16 +24712,19 @@
         </is>
       </c>
       <c r="E794">
-        <v>9.199999999999999</v>
+        <v>7.44</v>
+      </c>
+      <c r="F794">
+        <v>-3.5</v>
       </c>
       <c r="G794" s="2">
-        <v>46113</v>
+        <v>46143</v>
       </c>
     </row>
     <row r="795">
       <c r="A795" t="inlineStr">
         <is>
-          <t>Jaraguá do Sul</t>
+          <t>Indaial</t>
         </is>
       </c>
       <c r="B795" t="inlineStr">
@@ -24695,7 +24734,7 @@
       </c>
       <c r="C795" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D795" t="inlineStr">
@@ -24704,16 +24743,16 @@
         </is>
       </c>
       <c r="E795">
-        <v>3.3</v>
+        <v>3.72</v>
       </c>
       <c r="G795" s="2">
-        <v>46082</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="796">
       <c r="A796" t="inlineStr">
         <is>
-          <t>Jaraguá do Sul</t>
+          <t>Indaial</t>
         </is>
       </c>
       <c r="B796" t="inlineStr">
@@ -24723,7 +24762,7 @@
       </c>
       <c r="C796" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D796" t="inlineStr">
@@ -24732,16 +24771,16 @@
         </is>
       </c>
       <c r="E796">
-        <v>4.35</v>
+        <v>3.75</v>
       </c>
       <c r="G796" s="2">
-        <v>46082</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="797">
       <c r="A797" t="inlineStr">
         <is>
-          <t>Jaraguá do Sul</t>
+          <t>Indaial</t>
         </is>
       </c>
       <c r="B797" t="inlineStr">
@@ -24751,7 +24790,7 @@
       </c>
       <c r="C797" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D797" t="inlineStr">
@@ -24760,16 +24799,16 @@
         </is>
       </c>
       <c r="E797">
-        <v>5.98</v>
+        <v>6.18</v>
       </c>
       <c r="G797" s="2">
-        <v>46082</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="798">
       <c r="A798" t="inlineStr">
         <is>
-          <t>Jaraguá do Sul</t>
+          <t>Indaial</t>
         </is>
       </c>
       <c r="B798" t="inlineStr">
@@ -24779,7 +24818,7 @@
       </c>
       <c r="C798" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D798" t="inlineStr">
@@ -24788,16 +24827,16 @@
         </is>
       </c>
       <c r="E798">
-        <v>5.39</v>
+        <v>4.26</v>
       </c>
       <c r="G798" s="2">
-        <v>46082</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="799">
       <c r="A799" t="inlineStr">
         <is>
-          <t>Jaraguá do Sul</t>
+          <t>Indaial</t>
         </is>
       </c>
       <c r="B799" t="inlineStr">
@@ -24807,7 +24846,7 @@
       </c>
       <c r="C799" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D799" t="inlineStr">
@@ -24816,16 +24855,16 @@
         </is>
       </c>
       <c r="E799">
-        <v>27.43</v>
+        <v>28.61</v>
       </c>
       <c r="G799" s="2">
-        <v>46082</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="800">
       <c r="A800" t="inlineStr">
         <is>
-          <t>Jaraguá do Sul</t>
+          <t>Indaial</t>
         </is>
       </c>
       <c r="B800" t="inlineStr">
@@ -24835,7 +24874,7 @@
       </c>
       <c r="C800" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D800" t="inlineStr">
@@ -24844,16 +24883,16 @@
         </is>
       </c>
       <c r="E800">
-        <v>52.27</v>
+        <v>52.79</v>
       </c>
       <c r="G800" s="2">
-        <v>46082</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="801">
       <c r="A801" t="inlineStr">
         <is>
-          <t>Jaraguá do Sul</t>
+          <t>Indaial</t>
         </is>
       </c>
       <c r="B801" t="inlineStr">
@@ -24863,7 +24902,7 @@
       </c>
       <c r="C801" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D801" t="inlineStr">
@@ -24872,16 +24911,16 @@
         </is>
       </c>
       <c r="E801">
-        <v>3.33</v>
+        <v>3.41</v>
       </c>
       <c r="G801" s="2">
-        <v>46082</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="802">
       <c r="A802" t="inlineStr">
         <is>
-          <t>Jaraguá do Sul</t>
+          <t>Indaial</t>
         </is>
       </c>
       <c r="B802" t="inlineStr">
@@ -24891,7 +24930,7 @@
       </c>
       <c r="C802" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D802" t="inlineStr">
@@ -24900,16 +24939,16 @@
         </is>
       </c>
       <c r="E802">
-        <v>5.3</v>
+        <v>5.12</v>
       </c>
       <c r="G802" s="2">
-        <v>46082</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="803">
       <c r="A803" t="inlineStr">
         <is>
-          <t>Jaraguá do Sul</t>
+          <t>Indaial</t>
         </is>
       </c>
       <c r="B803" t="inlineStr">
@@ -24919,7 +24958,7 @@
       </c>
       <c r="C803" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D803" t="inlineStr">
@@ -24928,16 +24967,16 @@
         </is>
       </c>
       <c r="E803">
-        <v>3.81</v>
+        <v>3.8</v>
       </c>
       <c r="G803" s="2">
-        <v>46082</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="804">
       <c r="A804" t="inlineStr">
         <is>
-          <t>Jaraguá do Sul</t>
+          <t>Indaial</t>
         </is>
       </c>
       <c r="B804" t="inlineStr">
@@ -24947,7 +24986,7 @@
       </c>
       <c r="C804" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D804" t="inlineStr">
@@ -24956,16 +24995,16 @@
         </is>
       </c>
       <c r="E804">
-        <v>27.32</v>
+        <v>26.67</v>
       </c>
       <c r="G804" s="2">
-        <v>46082</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="805">
       <c r="A805" t="inlineStr">
         <is>
-          <t>Jaraguá do Sul</t>
+          <t>Indaial</t>
         </is>
       </c>
       <c r="B805" t="inlineStr">
@@ -24975,7 +25014,7 @@
       </c>
       <c r="C805" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D805" t="inlineStr">
@@ -24984,16 +25023,16 @@
         </is>
       </c>
       <c r="E805">
-        <v>15.57</v>
+        <v>13.35</v>
       </c>
       <c r="G805" s="2">
-        <v>46082</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="806">
       <c r="A806" t="inlineStr">
         <is>
-          <t>Jaraguá do Sul</t>
+          <t>Indaial</t>
         </is>
       </c>
       <c r="B806" t="inlineStr">
@@ -25003,7 +25042,7 @@
       </c>
       <c r="C806" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D806" t="inlineStr">
@@ -25012,16 +25051,16 @@
         </is>
       </c>
       <c r="E806">
-        <v>10.32</v>
+        <v>12.98</v>
       </c>
       <c r="G806" s="2">
-        <v>46082</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="807">
       <c r="A807" t="inlineStr">
         <is>
-          <t>Jaraguá do Sul</t>
+          <t>Indaial</t>
         </is>
       </c>
       <c r="B807" t="inlineStr">
@@ -25031,7 +25070,7 @@
       </c>
       <c r="C807" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D807" t="inlineStr">
@@ -25040,10 +25079,10 @@
         </is>
       </c>
       <c r="E807">
-        <v>7.84</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G807" s="2">
-        <v>46082</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="808">
@@ -25059,7 +25098,7 @@
       </c>
       <c r="C808" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D808" t="inlineStr">
@@ -25068,13 +25107,10 @@
         </is>
       </c>
       <c r="E808">
-        <v>3.39</v>
-      </c>
-      <c r="F808">
-        <v>2.73</v>
+        <v>3.3</v>
       </c>
       <c r="G808" s="2">
-        <v>46113</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="809">
@@ -25090,7 +25126,7 @@
       </c>
       <c r="C809" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D809" t="inlineStr">
@@ -25099,13 +25135,10 @@
         </is>
       </c>
       <c r="E809">
-        <v>4.44</v>
-      </c>
-      <c r="F809">
-        <v>2.07</v>
+        <v>4.35</v>
       </c>
       <c r="G809" s="2">
-        <v>46113</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="810">
@@ -25121,7 +25154,7 @@
       </c>
       <c r="C810" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D810" t="inlineStr">
@@ -25130,13 +25163,10 @@
         </is>
       </c>
       <c r="E810">
-        <v>6.56</v>
-      </c>
-      <c r="F810">
-        <v>9.699999999999999</v>
+        <v>5.98</v>
       </c>
       <c r="G810" s="2">
-        <v>46113</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="811">
@@ -25152,7 +25182,7 @@
       </c>
       <c r="C811" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D811" t="inlineStr">
@@ -25161,13 +25191,10 @@
         </is>
       </c>
       <c r="E811">
-        <v>5.52</v>
-      </c>
-      <c r="F811">
-        <v>2.41</v>
+        <v>5.39</v>
       </c>
       <c r="G811" s="2">
-        <v>46113</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="812">
@@ -25183,7 +25210,7 @@
       </c>
       <c r="C812" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D812" t="inlineStr">
@@ -25192,13 +25219,10 @@
         </is>
       </c>
       <c r="E812">
-        <v>27.95</v>
-      </c>
-      <c r="F812">
-        <v>1.9</v>
+        <v>27.43</v>
       </c>
       <c r="G812" s="2">
-        <v>46113</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="813">
@@ -25214,7 +25238,7 @@
       </c>
       <c r="C813" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D813" t="inlineStr">
@@ -25223,13 +25247,10 @@
         </is>
       </c>
       <c r="E813">
-        <v>55.33</v>
-      </c>
-      <c r="F813">
-        <v>5.85</v>
+        <v>52.27</v>
       </c>
       <c r="G813" s="2">
-        <v>46113</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="814">
@@ -25245,7 +25266,7 @@
       </c>
       <c r="C814" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D814" t="inlineStr">
@@ -25254,13 +25275,10 @@
         </is>
       </c>
       <c r="E814">
-        <v>3.45</v>
-      </c>
-      <c r="F814">
-        <v>3.6</v>
+        <v>3.33</v>
       </c>
       <c r="G814" s="2">
-        <v>46113</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="815">
@@ -25276,7 +25294,7 @@
       </c>
       <c r="C815" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D815" t="inlineStr">
@@ -25285,13 +25303,10 @@
         </is>
       </c>
       <c r="E815">
-        <v>5.38</v>
-      </c>
-      <c r="F815">
-        <v>1.51</v>
+        <v>5.3</v>
       </c>
       <c r="G815" s="2">
-        <v>46113</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="816">
@@ -25307,7 +25322,7 @@
       </c>
       <c r="C816" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D816" t="inlineStr">
@@ -25316,13 +25331,10 @@
         </is>
       </c>
       <c r="E816">
-        <v>4.22</v>
-      </c>
-      <c r="F816">
-        <v>10.76</v>
+        <v>3.81</v>
       </c>
       <c r="G816" s="2">
-        <v>46113</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="817">
@@ -25338,7 +25350,7 @@
       </c>
       <c r="C817" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D817" t="inlineStr">
@@ -25347,13 +25359,10 @@
         </is>
       </c>
       <c r="E817">
-        <v>28.1</v>
-      </c>
-      <c r="F817">
-        <v>2.86</v>
+        <v>27.32</v>
       </c>
       <c r="G817" s="2">
-        <v>46113</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="818">
@@ -25369,7 +25378,7 @@
       </c>
       <c r="C818" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D818" t="inlineStr">
@@ -25378,13 +25387,10 @@
         </is>
       </c>
       <c r="E818">
-        <v>15.9</v>
-      </c>
-      <c r="F818">
-        <v>2.12</v>
+        <v>15.57</v>
       </c>
       <c r="G818" s="2">
-        <v>46113</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="819">
@@ -25400,7 +25406,7 @@
       </c>
       <c r="C819" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D819" t="inlineStr">
@@ -25409,13 +25415,10 @@
         </is>
       </c>
       <c r="E819">
-        <v>10.65</v>
-      </c>
-      <c r="F819">
-        <v>3.2</v>
+        <v>10.32</v>
       </c>
       <c r="G819" s="2">
-        <v>46113</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="820">
@@ -25431,7 +25434,7 @@
       </c>
       <c r="C820" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D820" t="inlineStr">
@@ -25440,19 +25443,16 @@
         </is>
       </c>
       <c r="E820">
-        <v>7.99</v>
-      </c>
-      <c r="F820">
-        <v>1.91</v>
+        <v>7.84</v>
       </c>
       <c r="G820" s="2">
-        <v>46113</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="821">
       <c r="A821" t="inlineStr">
         <is>
-          <t>Massaranduba</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B821" t="inlineStr">
@@ -25473,6 +25473,9 @@
       <c r="E821">
         <v>3.39</v>
       </c>
+      <c r="F821">
+        <v>2.73</v>
+      </c>
       <c r="G821" s="2">
         <v>46113</v>
       </c>
@@ -25480,7 +25483,7 @@
     <row r="822">
       <c r="A822" t="inlineStr">
         <is>
-          <t>Massaranduba</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B822" t="inlineStr">
@@ -25499,7 +25502,10 @@
         </is>
       </c>
       <c r="E822">
-        <v>3.69</v>
+        <v>4.44</v>
+      </c>
+      <c r="F822">
+        <v>2.07</v>
       </c>
       <c r="G822" s="2">
         <v>46113</v>
@@ -25508,7 +25514,7 @@
     <row r="823">
       <c r="A823" t="inlineStr">
         <is>
-          <t>Massaranduba</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B823" t="inlineStr">
@@ -25527,7 +25533,10 @@
         </is>
       </c>
       <c r="E823">
-        <v>6.07</v>
+        <v>6.56</v>
+      </c>
+      <c r="F823">
+        <v>9.699999999999999</v>
       </c>
       <c r="G823" s="2">
         <v>46113</v>
@@ -25536,7 +25545,7 @@
     <row r="824">
       <c r="A824" t="inlineStr">
         <is>
-          <t>Massaranduba</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B824" t="inlineStr">
@@ -25555,7 +25564,10 @@
         </is>
       </c>
       <c r="E824">
-        <v>3.83</v>
+        <v>5.52</v>
+      </c>
+      <c r="F824">
+        <v>2.41</v>
       </c>
       <c r="G824" s="2">
         <v>46113</v>
@@ -25564,7 +25576,7 @@
     <row r="825">
       <c r="A825" t="inlineStr">
         <is>
-          <t>Massaranduba</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B825" t="inlineStr">
@@ -25583,7 +25595,10 @@
         </is>
       </c>
       <c r="E825">
-        <v>28.97</v>
+        <v>27.95</v>
+      </c>
+      <c r="F825">
+        <v>1.9</v>
       </c>
       <c r="G825" s="2">
         <v>46113</v>
@@ -25592,7 +25607,7 @@
     <row r="826">
       <c r="A826" t="inlineStr">
         <is>
-          <t>Massaranduba</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B826" t="inlineStr">
@@ -25611,7 +25626,10 @@
         </is>
       </c>
       <c r="E826">
-        <v>43.38</v>
+        <v>55.33</v>
+      </c>
+      <c r="F826">
+        <v>5.85</v>
       </c>
       <c r="G826" s="2">
         <v>46113</v>
@@ -25620,7 +25638,7 @@
     <row r="827">
       <c r="A827" t="inlineStr">
         <is>
-          <t>Massaranduba</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B827" t="inlineStr">
@@ -25639,7 +25657,10 @@
         </is>
       </c>
       <c r="E827">
-        <v>3.7</v>
+        <v>3.45</v>
+      </c>
+      <c r="F827">
+        <v>3.6</v>
       </c>
       <c r="G827" s="2">
         <v>46113</v>
@@ -25648,7 +25669,7 @@
     <row r="828">
       <c r="A828" t="inlineStr">
         <is>
-          <t>Massaranduba</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B828" t="inlineStr">
@@ -25667,7 +25688,10 @@
         </is>
       </c>
       <c r="E828">
-        <v>4.9</v>
+        <v>5.38</v>
+      </c>
+      <c r="F828">
+        <v>1.51</v>
       </c>
       <c r="G828" s="2">
         <v>46113</v>
@@ -25676,7 +25700,7 @@
     <row r="829">
       <c r="A829" t="inlineStr">
         <is>
-          <t>Massaranduba</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B829" t="inlineStr">
@@ -25695,7 +25719,10 @@
         </is>
       </c>
       <c r="E829">
-        <v>3.78</v>
+        <v>4.22</v>
+      </c>
+      <c r="F829">
+        <v>10.76</v>
       </c>
       <c r="G829" s="2">
         <v>46113</v>
@@ -25704,7 +25731,7 @@
     <row r="830">
       <c r="A830" t="inlineStr">
         <is>
-          <t>Massaranduba</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B830" t="inlineStr">
@@ -25723,7 +25750,10 @@
         </is>
       </c>
       <c r="E830">
-        <v>23.95</v>
+        <v>28.1</v>
+      </c>
+      <c r="F830">
+        <v>2.86</v>
       </c>
       <c r="G830" s="2">
         <v>46113</v>
@@ -25732,7 +25762,7 @@
     <row r="831">
       <c r="A831" t="inlineStr">
         <is>
-          <t>Massaranduba</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B831" t="inlineStr">
@@ -25751,7 +25781,10 @@
         </is>
       </c>
       <c r="E831">
-        <v>14.2</v>
+        <v>15.9</v>
+      </c>
+      <c r="F831">
+        <v>2.12</v>
       </c>
       <c r="G831" s="2">
         <v>46113</v>
@@ -25760,7 +25793,7 @@
     <row r="832">
       <c r="A832" t="inlineStr">
         <is>
-          <t>Massaranduba</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B832" t="inlineStr">
@@ -25779,7 +25812,10 @@
         </is>
       </c>
       <c r="E832">
-        <v>8.130000000000001</v>
+        <v>10.65</v>
+      </c>
+      <c r="F832">
+        <v>3.2</v>
       </c>
       <c r="G832" s="2">
         <v>46113</v>
@@ -25788,7 +25824,7 @@
     <row r="833">
       <c r="A833" t="inlineStr">
         <is>
-          <t>Massaranduba</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B833" t="inlineStr">
@@ -25807,7 +25843,10 @@
         </is>
       </c>
       <c r="E833">
-        <v>6.69</v>
+        <v>7.99</v>
+      </c>
+      <c r="F833">
+        <v>1.91</v>
       </c>
       <c r="G833" s="2">
         <v>46113</v>
@@ -25816,7 +25855,7 @@
     <row r="834">
       <c r="A834" t="inlineStr">
         <is>
-          <t>Navegantes</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B834" t="inlineStr">
@@ -25835,7 +25874,7 @@
         </is>
       </c>
       <c r="E834">
-        <v>2.7</v>
+        <v>3.39</v>
       </c>
       <c r="G834" s="2">
         <v>46113</v>
@@ -25844,7 +25883,7 @@
     <row r="835">
       <c r="A835" t="inlineStr">
         <is>
-          <t>Navegantes</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B835" t="inlineStr">
@@ -25863,7 +25902,7 @@
         </is>
       </c>
       <c r="E835">
-        <v>3.72</v>
+        <v>3.69</v>
       </c>
       <c r="G835" s="2">
         <v>46113</v>
@@ -25872,7 +25911,7 @@
     <row r="836">
       <c r="A836" t="inlineStr">
         <is>
-          <t>Navegantes</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B836" t="inlineStr">
@@ -25891,7 +25930,7 @@
         </is>
       </c>
       <c r="E836">
-        <v>5.14</v>
+        <v>6.07</v>
       </c>
       <c r="G836" s="2">
         <v>46113</v>
@@ -25900,7 +25939,7 @@
     <row r="837">
       <c r="A837" t="inlineStr">
         <is>
-          <t>Navegantes</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B837" t="inlineStr">
@@ -25919,7 +25958,7 @@
         </is>
       </c>
       <c r="E837">
-        <v>4.39</v>
+        <v>3.83</v>
       </c>
       <c r="G837" s="2">
         <v>46113</v>
@@ -25928,7 +25967,7 @@
     <row r="838">
       <c r="A838" t="inlineStr">
         <is>
-          <t>Navegantes</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B838" t="inlineStr">
@@ -25947,7 +25986,7 @@
         </is>
       </c>
       <c r="E838">
-        <v>48.94</v>
+        <v>28.97</v>
       </c>
       <c r="G838" s="2">
         <v>46113</v>
@@ -25956,7 +25995,7 @@
     <row r="839">
       <c r="A839" t="inlineStr">
         <is>
-          <t>Navegantes</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B839" t="inlineStr">
@@ -25975,7 +26014,7 @@
         </is>
       </c>
       <c r="E839">
-        <v>55.07</v>
+        <v>43.38</v>
       </c>
       <c r="G839" s="2">
         <v>46113</v>
@@ -25984,7 +26023,7 @@
     <row r="840">
       <c r="A840" t="inlineStr">
         <is>
-          <t>Navegantes</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B840" t="inlineStr">
@@ -26003,7 +26042,7 @@
         </is>
       </c>
       <c r="E840">
-        <v>3.12</v>
+        <v>3.7</v>
       </c>
       <c r="G840" s="2">
         <v>46113</v>
@@ -26012,7 +26051,7 @@
     <row r="841">
       <c r="A841" t="inlineStr">
         <is>
-          <t>Navegantes</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B841" t="inlineStr">
@@ -26031,7 +26070,7 @@
         </is>
       </c>
       <c r="E841">
-        <v>4.84</v>
+        <v>4.9</v>
       </c>
       <c r="G841" s="2">
         <v>46113</v>
@@ -26040,7 +26079,7 @@
     <row r="842">
       <c r="A842" t="inlineStr">
         <is>
-          <t>Navegantes</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B842" t="inlineStr">
@@ -26059,7 +26098,7 @@
         </is>
       </c>
       <c r="E842">
-        <v>4.23</v>
+        <v>3.78</v>
       </c>
       <c r="G842" s="2">
         <v>46113</v>
@@ -26068,7 +26107,7 @@
     <row r="843">
       <c r="A843" t="inlineStr">
         <is>
-          <t>Navegantes</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B843" t="inlineStr">
@@ -26087,7 +26126,7 @@
         </is>
       </c>
       <c r="E843">
-        <v>13.96</v>
+        <v>23.95</v>
       </c>
       <c r="G843" s="2">
         <v>46113</v>
@@ -26096,7 +26135,7 @@
     <row r="844">
       <c r="A844" t="inlineStr">
         <is>
-          <t>Navegantes</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B844" t="inlineStr">
@@ -26115,7 +26154,7 @@
         </is>
       </c>
       <c r="E844">
-        <v>14.94</v>
+        <v>14.2</v>
       </c>
       <c r="G844" s="2">
         <v>46113</v>
@@ -26124,7 +26163,7 @@
     <row r="845">
       <c r="A845" t="inlineStr">
         <is>
-          <t>Navegantes</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B845" t="inlineStr">
@@ -26143,7 +26182,7 @@
         </is>
       </c>
       <c r="E845">
-        <v>8.24</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="G845" s="2">
         <v>46113</v>
@@ -26152,7 +26191,7 @@
     <row r="846">
       <c r="A846" t="inlineStr">
         <is>
-          <t>Navegantes</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B846" t="inlineStr">
@@ -26171,7 +26210,7 @@
         </is>
       </c>
       <c r="E846">
-        <v>8.460000000000001</v>
+        <v>6.69</v>
       </c>
       <c r="G846" s="2">
         <v>46113</v>
@@ -26180,7 +26219,7 @@
     <row r="847">
       <c r="A847" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Navegantes</t>
         </is>
       </c>
       <c r="B847" t="inlineStr">
@@ -26199,7 +26238,7 @@
         </is>
       </c>
       <c r="E847">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="G847" s="2">
         <v>46113</v>
@@ -26208,7 +26247,7 @@
     <row r="848">
       <c r="A848" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Navegantes</t>
         </is>
       </c>
       <c r="B848" t="inlineStr">
@@ -26227,7 +26266,7 @@
         </is>
       </c>
       <c r="E848">
-        <v>4.17</v>
+        <v>3.72</v>
       </c>
       <c r="G848" s="2">
         <v>46113</v>
@@ -26236,7 +26275,7 @@
     <row r="849">
       <c r="A849" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Navegantes</t>
         </is>
       </c>
       <c r="B849" t="inlineStr">
@@ -26255,7 +26294,7 @@
         </is>
       </c>
       <c r="E849">
-        <v>5.29</v>
+        <v>5.14</v>
       </c>
       <c r="G849" s="2">
         <v>46113</v>
@@ -26264,7 +26303,7 @@
     <row r="850">
       <c r="A850" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Navegantes</t>
         </is>
       </c>
       <c r="B850" t="inlineStr">
@@ -26283,7 +26322,7 @@
         </is>
       </c>
       <c r="E850">
-        <v>5.09</v>
+        <v>4.39</v>
       </c>
       <c r="G850" s="2">
         <v>46113</v>
@@ -26292,7 +26331,7 @@
     <row r="851">
       <c r="A851" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Navegantes</t>
         </is>
       </c>
       <c r="B851" t="inlineStr">
@@ -26311,7 +26350,7 @@
         </is>
       </c>
       <c r="E851">
-        <v>52.37</v>
+        <v>48.94</v>
       </c>
       <c r="G851" s="2">
         <v>46113</v>
@@ -26320,7 +26359,7 @@
     <row r="852">
       <c r="A852" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Navegantes</t>
         </is>
       </c>
       <c r="B852" t="inlineStr">
@@ -26339,7 +26378,7 @@
         </is>
       </c>
       <c r="E852">
-        <v>60.97</v>
+        <v>55.07</v>
       </c>
       <c r="G852" s="2">
         <v>46113</v>
@@ -26348,7 +26387,7 @@
     <row r="853">
       <c r="A853" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Navegantes</t>
         </is>
       </c>
       <c r="B853" t="inlineStr">
@@ -26367,7 +26406,7 @@
         </is>
       </c>
       <c r="E853">
-        <v>3.84</v>
+        <v>3.12</v>
       </c>
       <c r="G853" s="2">
         <v>46113</v>
@@ -26376,7 +26415,7 @@
     <row r="854">
       <c r="A854" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Navegantes</t>
         </is>
       </c>
       <c r="B854" t="inlineStr">
@@ -26395,7 +26434,7 @@
         </is>
       </c>
       <c r="E854">
-        <v>4.89</v>
+        <v>4.84</v>
       </c>
       <c r="G854" s="2">
         <v>46113</v>
@@ -26404,7 +26443,7 @@
     <row r="855">
       <c r="A855" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Navegantes</t>
         </is>
       </c>
       <c r="B855" t="inlineStr">
@@ -26423,7 +26462,7 @@
         </is>
       </c>
       <c r="E855">
-        <v>4.43</v>
+        <v>4.23</v>
       </c>
       <c r="G855" s="2">
         <v>46113</v>
@@ -26432,7 +26471,7 @@
     <row r="856">
       <c r="A856" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Navegantes</t>
         </is>
       </c>
       <c r="B856" t="inlineStr">
@@ -26451,7 +26490,7 @@
         </is>
       </c>
       <c r="E856">
-        <v>16.92</v>
+        <v>13.96</v>
       </c>
       <c r="G856" s="2">
         <v>46113</v>
@@ -26460,7 +26499,7 @@
     <row r="857">
       <c r="A857" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Navegantes</t>
         </is>
       </c>
       <c r="B857" t="inlineStr">
@@ -26479,7 +26518,7 @@
         </is>
       </c>
       <c r="E857">
-        <v>17.86</v>
+        <v>14.94</v>
       </c>
       <c r="G857" s="2">
         <v>46113</v>
@@ -26488,7 +26527,7 @@
     <row r="858">
       <c r="A858" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Navegantes</t>
         </is>
       </c>
       <c r="B858" t="inlineStr">
@@ -26507,7 +26546,7 @@
         </is>
       </c>
       <c r="E858">
-        <v>8.93</v>
+        <v>8.24</v>
       </c>
       <c r="G858" s="2">
         <v>46113</v>
@@ -26516,28 +26555,392 @@
     <row r="859">
       <c r="A859" t="inlineStr">
         <is>
+          <t>Navegantes</t>
+        </is>
+      </c>
+      <c r="B859" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C859" t="inlineStr">
+        <is>
+          <t>Abril</t>
+        </is>
+      </c>
+      <c r="D859" t="inlineStr">
+        <is>
+          <t>Óleo de Soja</t>
+        </is>
+      </c>
+      <c r="E859">
+        <v>8.460000000000001</v>
+      </c>
+      <c r="G859" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" t="inlineStr">
+        <is>
           <t>Timbó</t>
         </is>
       </c>
-      <c r="B859" t="inlineStr">
+      <c r="B860" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="C859" t="inlineStr">
+      <c r="C860" t="inlineStr">
         <is>
           <t>Abril</t>
         </is>
       </c>
-      <c r="D859" t="inlineStr">
+      <c r="D860" t="inlineStr">
+        <is>
+          <t>Arroz tipo 1</t>
+        </is>
+      </c>
+      <c r="E860">
+        <v>2.63</v>
+      </c>
+      <c r="G860" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" t="inlineStr">
+        <is>
+          <t>Timbó</t>
+        </is>
+      </c>
+      <c r="B861" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C861" t="inlineStr">
+        <is>
+          <t>Abril</t>
+        </is>
+      </c>
+      <c r="D861" t="inlineStr">
+        <is>
+          <t>Açúcar Refinado</t>
+        </is>
+      </c>
+      <c r="E861">
+        <v>4.17</v>
+      </c>
+      <c r="G861" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" t="inlineStr">
+        <is>
+          <t>Timbó</t>
+        </is>
+      </c>
+      <c r="B862" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C862" t="inlineStr">
+        <is>
+          <t>Abril</t>
+        </is>
+      </c>
+      <c r="D862" t="inlineStr">
+        <is>
+          <t>Banana</t>
+        </is>
+      </c>
+      <c r="E862">
+        <v>5.29</v>
+      </c>
+      <c r="G862" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" t="inlineStr">
+        <is>
+          <t>Timbó</t>
+        </is>
+      </c>
+      <c r="B863" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C863" t="inlineStr">
+        <is>
+          <t>Abril</t>
+        </is>
+      </c>
+      <c r="D863" t="inlineStr">
+        <is>
+          <t>Batata</t>
+        </is>
+      </c>
+      <c r="E863">
+        <v>5.09</v>
+      </c>
+      <c r="G863" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" t="inlineStr">
+        <is>
+          <t>Timbó</t>
+        </is>
+      </c>
+      <c r="B864" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C864" t="inlineStr">
+        <is>
+          <t>Abril</t>
+        </is>
+      </c>
+      <c r="D864" t="inlineStr">
+        <is>
+          <t>Café em pó</t>
+        </is>
+      </c>
+      <c r="E864">
+        <v>52.37</v>
+      </c>
+      <c r="G864" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" t="inlineStr">
+        <is>
+          <t>Timbó</t>
+        </is>
+      </c>
+      <c r="B865" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C865" t="inlineStr">
+        <is>
+          <t>Abril</t>
+        </is>
+      </c>
+      <c r="D865" t="inlineStr">
+        <is>
+          <t>Carne</t>
+        </is>
+      </c>
+      <c r="E865">
+        <v>60.97</v>
+      </c>
+      <c r="G865" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" t="inlineStr">
+        <is>
+          <t>Timbó</t>
+        </is>
+      </c>
+      <c r="B866" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C866" t="inlineStr">
+        <is>
+          <t>Abril</t>
+        </is>
+      </c>
+      <c r="D866" t="inlineStr">
+        <is>
+          <t>Farinha de Trigo</t>
+        </is>
+      </c>
+      <c r="E866">
+        <v>3.84</v>
+      </c>
+      <c r="G866" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" t="inlineStr">
+        <is>
+          <t>Timbó</t>
+        </is>
+      </c>
+      <c r="B867" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C867" t="inlineStr">
+        <is>
+          <t>Abril</t>
+        </is>
+      </c>
+      <c r="D867" t="inlineStr">
+        <is>
+          <t>Feijão Preto</t>
+        </is>
+      </c>
+      <c r="E867">
+        <v>4.89</v>
+      </c>
+      <c r="G867" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" t="inlineStr">
+        <is>
+          <t>Timbó</t>
+        </is>
+      </c>
+      <c r="B868" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C868" t="inlineStr">
+        <is>
+          <t>Abril</t>
+        </is>
+      </c>
+      <c r="D868" t="inlineStr">
+        <is>
+          <t>Leite</t>
+        </is>
+      </c>
+      <c r="E868">
+        <v>4.43</v>
+      </c>
+      <c r="G868" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" t="inlineStr">
+        <is>
+          <t>Timbó</t>
+        </is>
+      </c>
+      <c r="B869" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C869" t="inlineStr">
+        <is>
+          <t>Abril</t>
+        </is>
+      </c>
+      <c r="D869" t="inlineStr">
+        <is>
+          <t>Manteiga</t>
+        </is>
+      </c>
+      <c r="E869">
+        <v>16.92</v>
+      </c>
+      <c r="G869" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" t="inlineStr">
+        <is>
+          <t>Timbó</t>
+        </is>
+      </c>
+      <c r="B870" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C870" t="inlineStr">
+        <is>
+          <t>Abril</t>
+        </is>
+      </c>
+      <c r="D870" t="inlineStr">
+        <is>
+          <t>Pão Francês</t>
+        </is>
+      </c>
+      <c r="E870">
+        <v>17.86</v>
+      </c>
+      <c r="G870" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" t="inlineStr">
+        <is>
+          <t>Timbó</t>
+        </is>
+      </c>
+      <c r="B871" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C871" t="inlineStr">
+        <is>
+          <t>Abril</t>
+        </is>
+      </c>
+      <c r="D871" t="inlineStr">
+        <is>
+          <t>Tomate</t>
+        </is>
+      </c>
+      <c r="E871">
+        <v>8.93</v>
+      </c>
+      <c r="G871" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" t="inlineStr">
+        <is>
+          <t>Timbó</t>
+        </is>
+      </c>
+      <c r="B872" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C872" t="inlineStr">
+        <is>
+          <t>Abril</t>
+        </is>
+      </c>
+      <c r="D872" t="inlineStr">
         <is>
           <t>Óleo de Soja</t>
         </is>
       </c>
-      <c r="E859">
+      <c r="E872">
         <v>8.67</v>
       </c>
-      <c r="G859" s="2">
+      <c r="G872" s="2">
         <v>46113</v>
       </c>
     </row>
